--- a/output/pdf_financials_xlsx/PESO.xlsx
+++ b/output/pdf_financials_xlsx/PESO.xlsx
@@ -3660,19 +3660,19 @@
         <v>0.101363</v>
       </c>
       <c r="F92" s="3" t="n">
-        <v>0</v>
+        <v>0.588684</v>
       </c>
       <c r="G92" s="3" t="n">
-        <v>0</v>
+        <v>4.45798</v>
       </c>
       <c r="H92" s="3" t="n">
-        <v>0</v>
+        <v>6.159786</v>
       </c>
       <c r="I92" s="3" t="n">
-        <v>0</v>
+        <v>6.157606</v>
       </c>
       <c r="J92" s="3" t="n">
-        <v>0</v>
+        <v>10.19224</v>
       </c>
     </row>
     <row r="93">
@@ -6849,7 +6849,11 @@
           <t>Warrants reserve (Note 12)</t>
         </is>
       </c>
-      <c r="D28" t="inlineStr"/>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E28" t="inlineStr">
         <is>
           <t>-</t>
@@ -7282,7 +7286,11 @@
           <t>Warrants reserve (Note 12)</t>
         </is>
       </c>
-      <c r="D35" t="inlineStr"/>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E35" t="inlineStr">
         <is>
           <t>-</t>
@@ -8508,7 +8516,11 @@
           <t>Warrants reserve (Note 14)</t>
         </is>
       </c>
-      <c r="D55" t="inlineStr"/>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E55" t="inlineStr">
         <is>
           <t>-</t>
@@ -9301,7 +9313,11 @@
           <t>Warrants reserve (Note 13)</t>
         </is>
       </c>
-      <c r="D68" t="inlineStr"/>
+      <c r="D68" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E68" t="inlineStr">
         <is>
           <t>-</t>

--- a/output/pdf_financials_xlsx/PESO.xlsx
+++ b/output/pdf_financials_xlsx/PESO.xlsx
@@ -1622,19 +1622,19 @@
         <v>0</v>
       </c>
       <c r="F34" s="3" t="n">
-        <v>0</v>
+        <v>0.89103</v>
       </c>
       <c r="G34" s="3" t="n">
-        <v>0</v>
+        <v>3.019481</v>
       </c>
       <c r="H34" s="3" t="n">
-        <v>0</v>
+        <v>0.901553</v>
       </c>
       <c r="I34" s="3" t="n">
-        <v>0</v>
+        <v>0.633233</v>
       </c>
       <c r="J34" s="3" t="n">
-        <v>0</v>
+        <v>4.849795</v>
       </c>
     </row>
     <row r="35">
@@ -1690,19 +1690,19 @@
         <v>0</v>
       </c>
       <c r="F36" s="3" t="n">
-        <v>0</v>
+        <v>0.89103</v>
       </c>
       <c r="G36" s="3" t="n">
-        <v>0</v>
+        <v>3.019481</v>
       </c>
       <c r="H36" s="3" t="n">
-        <v>0</v>
+        <v>0.901553</v>
       </c>
       <c r="I36" s="3" t="n">
-        <v>0</v>
+        <v>0.633233</v>
       </c>
       <c r="J36" s="3" t="n">
-        <v>0</v>
+        <v>4.849795</v>
       </c>
     </row>
     <row r="37">
@@ -2098,19 +2098,19 @@
         <v>0</v>
       </c>
       <c r="F48" s="3" t="n">
-        <v>7.128107</v>
+        <v>6.237077</v>
       </c>
       <c r="G48" s="3" t="n">
-        <v>3.160663</v>
+        <v>0.141182</v>
       </c>
       <c r="H48" s="3" t="n">
-        <v>2.246968</v>
+        <v>1.345415</v>
       </c>
       <c r="I48" s="3" t="n">
-        <v>2.049582</v>
+        <v>1.416349</v>
       </c>
       <c r="J48" s="3" t="n">
-        <v>6.762904</v>
+        <v>1.913109</v>
       </c>
     </row>
     <row r="49">
@@ -4781,19 +4781,19 @@
         <v>0</v>
       </c>
       <c r="F124" s="3" t="n">
-        <v>0</v>
+        <v>-1.235463</v>
       </c>
       <c r="G124" s="3" t="n">
-        <v>0</v>
+        <v>-1.907443</v>
       </c>
       <c r="H124" s="3" t="n">
-        <v>0</v>
+        <v>-2.58719</v>
       </c>
       <c r="I124" s="3" t="n">
-        <v>0</v>
+        <v>-2.773174</v>
       </c>
       <c r="J124" s="3" t="n">
-        <v>0</v>
+        <v>-3.462632</v>
       </c>
     </row>
     <row r="125">
@@ -4817,19 +4817,19 @@
         <v>0</v>
       </c>
       <c r="F125" s="3" t="n">
-        <v>0</v>
+        <v>-1.235463</v>
       </c>
       <c r="G125" s="3" t="n">
-        <v>0</v>
+        <v>-1.907443</v>
       </c>
       <c r="H125" s="3" t="n">
-        <v>0</v>
+        <v>-2.58719</v>
       </c>
       <c r="I125" s="3" t="n">
-        <v>0</v>
+        <v>-2.773174</v>
       </c>
       <c r="J125" s="3" t="n">
-        <v>0</v>
+        <v>-3.462632</v>
       </c>
     </row>
     <row r="126">
@@ -5317,7 +5317,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -11980,7 +11980,11 @@
           <t>Lease payments (Note 9)</t>
         </is>
       </c>
-      <c r="D113" t="inlineStr"/>
+      <c r="D113" t="inlineStr">
+        <is>
+          <t>RepaymentOfDebt</t>
+        </is>
+      </c>
       <c r="E113" t="inlineStr">
         <is>
           <t>-</t>
@@ -13235,7 +13239,11 @@
           <t>Lease payments (Note 9)</t>
         </is>
       </c>
-      <c r="D134" t="inlineStr"/>
+      <c r="D134" t="inlineStr">
+        <is>
+          <t>RepaymentOfDebt</t>
+        </is>
+      </c>
       <c r="E134" t="inlineStr">
         <is>
           <t>-</t>
@@ -15053,7 +15061,11 @@
           <t>Lease payments (Note 10)</t>
         </is>
       </c>
-      <c r="D164" t="inlineStr"/>
+      <c r="D164" t="inlineStr">
+        <is>
+          <t>RepaymentOfDebt</t>
+        </is>
+      </c>
       <c r="E164" t="inlineStr">
         <is>
           <t>-</t>

--- a/output/pdf_financials_xlsx/PESO.xlsx
+++ b/output/pdf_financials_xlsx/PESO.xlsx
@@ -3913,19 +3913,19 @@
         <v>0</v>
       </c>
       <c r="F100" s="3" t="n">
-        <v>1.444497</v>
+        <v>1.174675</v>
       </c>
       <c r="G100" s="3" t="n">
-        <v>1.947552</v>
+        <v>1.331828</v>
       </c>
       <c r="H100" s="3" t="n">
-        <v>1.979931</v>
+        <v>1.640576</v>
       </c>
       <c r="I100" s="3" t="n">
-        <v>1.545621</v>
+        <v>1.747176</v>
       </c>
       <c r="J100" s="3" t="n">
-        <v>1.19656</v>
+        <v>2.160861</v>
       </c>
     </row>
     <row r="101">
@@ -10523,7 +10523,11 @@
           <t>Depreciation, right-of-use assets (Note 9)</t>
         </is>
       </c>
-      <c r="D88" t="inlineStr"/>
+      <c r="D88" t="inlineStr">
+        <is>
+          <t>DepreciationAmortizationDepletion</t>
+        </is>
+      </c>
       <c r="E88" t="inlineStr">
         <is>
           <t>-</t>
@@ -13798,7 +13802,11 @@
           <t>Depreciation, right-of-use assets (Note 10)</t>
         </is>
       </c>
-      <c r="D143" t="inlineStr"/>
+      <c r="D143" t="inlineStr">
+        <is>
+          <t>DepreciationAmortizationDepletion</t>
+        </is>
+      </c>
       <c r="E143" t="inlineStr">
         <is>
           <t>-</t>

--- a/output/pdf_financials_xlsx/PESO.xlsx
+++ b/output/pdf_financials_xlsx/PESO.xlsx
@@ -525,10 +525,8 @@
       <c r="D4" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="E4" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="E4" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="F4" s="3" t="n">
         <v>9.350177</v>
@@ -561,10 +559,8 @@
       <c r="D5" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="E5" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="E5" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="F5" s="3" t="n">
         <v>7.819155</v>
@@ -597,10 +593,8 @@
       <c r="D6" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="E6" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="E6" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="F6" s="3" t="n">
         <v>1.531022</v>
@@ -633,10 +627,8 @@
       <c r="D7" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="E7" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="E7" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="F7" s="3" t="n">
         <v>0</v>
@@ -669,10 +661,8 @@
       <c r="D8" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="E8" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="E8" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="F8" s="3" t="n">
         <v>0</v>
@@ -705,10 +695,8 @@
       <c r="D9" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="E9" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="E9" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="F9" s="3" t="n">
         <v>0</v>
@@ -741,10 +729,8 @@
       <c r="D10" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="E10" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="E10" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="F10" s="3" t="n">
         <v>6.18519</v>
@@ -777,10 +763,8 @@
       <c r="D11" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="E11" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="E11" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="F11" s="3" t="n">
         <v>-7.27334</v>
@@ -813,10 +797,8 @@
       <c r="D12" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="E12" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="E12" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="F12" s="3" t="n">
         <v>0</v>
@@ -849,10 +831,8 @@
       <c r="D13" s="3" t="n">
         <v>-0</v>
       </c>
-      <c r="E13" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="E13" s="3" t="n">
+        <v>-0</v>
       </c>
       <c r="F13" s="3" t="n">
         <v>-0</v>
@@ -885,10 +865,8 @@
       <c r="D14" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="E14" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="E14" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="F14" s="3" t="n">
         <v>0</v>
@@ -921,10 +899,8 @@
       <c r="D15" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="E15" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="E15" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="F15" s="3" t="n">
         <v>0</v>
@@ -957,10 +933,8 @@
       <c r="D16" s="3" t="n">
         <v>-0.15933</v>
       </c>
-      <c r="E16" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="E16" s="3" t="n">
+        <v>-0.597935</v>
       </c>
       <c r="F16" s="3" t="n">
         <v>-11.072814</v>
@@ -993,10 +967,8 @@
       <c r="D17" s="3" t="n">
         <v>-0</v>
       </c>
-      <c r="E17" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="E17" s="3" t="n">
+        <v>-0</v>
       </c>
       <c r="F17" s="3" t="n">
         <v>-0</v>
@@ -1133,10 +1105,8 @@
       <c r="D20" s="3" t="n">
         <v>-0.15933</v>
       </c>
-      <c r="E20" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="E20" s="3" t="n">
+        <v>-0.597935</v>
       </c>
       <c r="F20" s="3" t="n">
         <v>-11.072814</v>
@@ -1169,10 +1139,8 @@
       <c r="D21" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="E21" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="E21" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="F21" s="3" t="n">
         <v>0</v>
@@ -1205,10 +1173,8 @@
       <c r="D22" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="E22" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="E22" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="F22" s="3" t="n">
         <v>0</v>
@@ -1275,10 +1241,8 @@
       <c r="D24" s="3" t="n">
         <v>-0.16</v>
       </c>
-      <c r="E24" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="E24" s="3" t="n">
+        <v>-0.36</v>
       </c>
       <c r="F24" s="3" t="n">
         <v>-0.23</v>
@@ -1311,10 +1275,8 @@
       <c r="D25" s="3" t="n">
         <v>-0.16</v>
       </c>
-      <c r="E25" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="E25" s="3" t="n">
+        <v>-0.36</v>
       </c>
       <c r="F25" s="3" t="n">
         <v>-0.23</v>
@@ -1347,10 +1309,8 @@
       <c r="D26" s="3" t="n">
         <v>0.995812</v>
       </c>
-      <c r="E26" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="E26" s="3" t="n">
+        <v>1.660931</v>
       </c>
       <c r="F26" s="3" t="n">
         <v>48.14267</v>
@@ -1383,10 +1343,8 @@
       <c r="D27" s="3" t="n">
         <v>-0.15933</v>
       </c>
-      <c r="E27" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="E27" s="3" t="n">
+        <v>-0.597935</v>
       </c>
       <c r="F27" s="3" t="n">
         <v>-11.072814</v>
@@ -1419,10 +1377,8 @@
       <c r="D28" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="E28" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="E28" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="F28" s="3" t="n">
         <v>2.619172</v>
@@ -1455,10 +1411,8 @@
       <c r="D29" s="3" t="n">
         <v>-0.15933</v>
       </c>
-      <c r="E29" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="E29" s="3" t="n">
+        <v>-0.597935</v>
       </c>
       <c r="F29" s="3" t="n">
         <v>-8.453642</v>
@@ -1533,10 +1487,8 @@
       <c r="D31" s="3" t="n">
         <v>-0</v>
       </c>
-      <c r="E31" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="E31" s="3" t="n">
+        <v>-0</v>
       </c>
       <c r="F31" s="3" t="n">
         <v>-0</v>
@@ -4489,19 +4441,19 @@
         <v>0</v>
       </c>
       <c r="F116" s="3" t="n">
-        <v>0</v>
+        <v>-0.015933</v>
       </c>
       <c r="G116" s="3" t="n">
-        <v>0</v>
+        <v>-0.01244</v>
       </c>
       <c r="H116" s="3" t="n">
-        <v>0</v>
+        <v>-0.032594</v>
       </c>
       <c r="I116" s="3" t="n">
-        <v>0</v>
+        <v>-0.076659</v>
       </c>
       <c r="J116" s="3" t="n">
-        <v>0</v>
+        <v>-0.044234</v>
       </c>
     </row>
     <row r="117">
@@ -5223,7 +5175,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M351"/>
+  <dimension ref="A1:M355"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -11510,7 +11462,11 @@
           <t>Purchase of intangible assets (Note 8)</t>
         </is>
       </c>
-      <c r="D105" t="inlineStr"/>
+      <c r="D105" t="inlineStr">
+        <is>
+          <t>NetIntangiblesPurchaseAndSale</t>
+        </is>
+      </c>
       <c r="E105" t="inlineStr">
         <is>
           <t>-</t>
@@ -14526,7 +14482,11 @@
           <t>Purchase of intangible assets (Note 9)</t>
         </is>
       </c>
-      <c r="D155" t="inlineStr"/>
+      <c r="D155" t="inlineStr">
+        <is>
+          <t>NetIntangiblesPurchaseAndSale</t>
+        </is>
+      </c>
       <c r="E155" t="inlineStr">
         <is>
           <t>-</t>
@@ -23710,28 +23670,36 @@
           <t>income_statement</t>
         </is>
       </c>
-      <c r="B307" t="inlineStr"/>
+      <c r="B307" t="inlineStr">
+        <is>
+          <t>Expenses</t>
+        </is>
+      </c>
       <c r="C307" t="inlineStr">
         <is>
-          <t>For the Years Ended December 31, 2020 and December</t>
-        </is>
-      </c>
-      <c r="D307" t="inlineStr"/>
+          <t>Professional fees</t>
+        </is>
+      </c>
+      <c r="D307" t="inlineStr">
+        <is>
+          <t>ProfessionalExpenseAndContractServicesExpense</t>
+        </is>
+      </c>
       <c r="E307" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="F307" s="5" t="n">
-        <v>0.002019</v>
+      <c r="F307" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="G307" s="5" t="n">
-        <v>3.1e-05</v>
-      </c>
-      <c r="H307" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>0.147144</v>
+      </c>
+      <c r="H307" s="5" t="n">
+        <v>0.546019</v>
       </c>
       <c r="I307" t="inlineStr">
         <is>
@@ -23765,28 +23733,28 @@
           <t>income_statement</t>
         </is>
       </c>
-      <c r="B308" t="inlineStr"/>
+      <c r="B308" t="inlineStr">
+        <is>
+          <t>Expenses</t>
+        </is>
+      </c>
       <c r="C308" t="inlineStr">
         <is>
-          <t>December 31, December</t>
+          <t>Listing fees</t>
         </is>
       </c>
       <c r="D308" t="inlineStr"/>
-      <c r="E308" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="E308" s="5" t="n">
+        <v>0.030864</v>
       </c>
       <c r="F308" s="5" t="n">
-        <v>0.002019</v>
+        <v>0.018848</v>
       </c>
       <c r="G308" s="5" t="n">
-        <v>3.1e-05</v>
-      </c>
-      <c r="H308" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>0.012186</v>
+      </c>
+      <c r="H308" s="5" t="n">
+        <v>0.051916</v>
       </c>
       <c r="I308" t="inlineStr">
         <is>
@@ -23827,27 +23795,29 @@
       </c>
       <c r="C309" t="inlineStr">
         <is>
-          <t>Professional Fees $</t>
+          <t>Net loss and comprehensive loss for the year</t>
         </is>
       </c>
       <c r="D309" t="inlineStr">
         <is>
-          <t>ProfessionalExpenseAndContractServicesExpense</t>
-        </is>
-      </c>
-      <c r="E309" s="5" t="n">
-        <v>0.138423</v>
-      </c>
-      <c r="F309" s="5" t="n">
-        <v>0.222292</v>
+          <t>NetIncome</t>
+        </is>
+      </c>
+      <c r="E309" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F309" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="G309" s="5" t="n">
-        <v>0.147144</v>
-      </c>
-      <c r="H309" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>-0.15933</v>
+      </c>
+      <c r="H309" s="5" t="n">
+        <v>-0.597935</v>
       </c>
       <c r="I309" t="inlineStr">
         <is>
@@ -23888,23 +23858,29 @@
       </c>
       <c r="C310" t="inlineStr">
         <is>
-          <t>Listing fees</t>
-        </is>
-      </c>
-      <c r="D310" t="inlineStr"/>
-      <c r="E310" s="5" t="n">
-        <v>0.030864</v>
-      </c>
-      <c r="F310" s="5" t="n">
-        <v>0.018848</v>
+          <t>Net loss per share - basic and diluted</t>
+        </is>
+      </c>
+      <c r="D310" t="inlineStr">
+        <is>
+          <t>BasicEPS</t>
+        </is>
+      </c>
+      <c r="E310" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F310" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="G310" s="5" t="n">
-        <v>0.012186</v>
-      </c>
-      <c r="H310" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>-1.6e-07</v>
+      </c>
+      <c r="H310" s="5" t="n">
+        <v>-3.6e-07</v>
       </c>
       <c r="I310" t="inlineStr">
         <is>
@@ -23945,29 +23921,25 @@
       </c>
       <c r="C311" t="inlineStr">
         <is>
-          <t>Net loss and comprehensive loss for the year $</t>
-        </is>
-      </c>
-      <c r="D311" t="inlineStr">
-        <is>
-          <t>NetIncome</t>
-        </is>
-      </c>
+          <t>Weighted average shares outstanding - basic and diluted</t>
+        </is>
+      </c>
+      <c r="D311" t="inlineStr"/>
       <c r="E311" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="F311" s="5" t="n">
-        <v>-0.24114</v>
+      <c r="F311" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="G311" s="5" t="n">
-        <v>-0.15933</v>
-      </c>
-      <c r="H311" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>1</v>
+      </c>
+      <c r="H311" s="5" t="n">
+        <v>1.657534</v>
       </c>
       <c r="I311" t="inlineStr">
         <is>
@@ -24001,31 +23973,23 @@
           <t>income_statement</t>
         </is>
       </c>
-      <c r="B312" t="inlineStr">
-        <is>
-          <t>Expenses</t>
-        </is>
-      </c>
+      <c r="B312" t="inlineStr"/>
       <c r="C312" t="inlineStr">
         <is>
-          <t>Net loss per share – basic and diluted $</t>
-        </is>
-      </c>
-      <c r="D312" t="inlineStr">
-        <is>
-          <t>BasicEPS</t>
-        </is>
-      </c>
+          <t>For the Years Ended December 31, 2020 and December</t>
+        </is>
+      </c>
+      <c r="D312" t="inlineStr"/>
       <c r="E312" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
       <c r="F312" s="5" t="n">
-        <v>-2.4e-07</v>
+        <v>0.002019</v>
       </c>
       <c r="G312" s="5" t="n">
-        <v>-1.6e-07</v>
+        <v>3.1e-05</v>
       </c>
       <c r="H312" t="inlineStr">
         <is>
@@ -24064,25 +24028,23 @@
           <t>income_statement</t>
         </is>
       </c>
-      <c r="B313" t="inlineStr">
-        <is>
-          <t>diluted</t>
-        </is>
-      </c>
+      <c r="B313" t="inlineStr"/>
       <c r="C313" t="inlineStr">
         <is>
-          <t>diluted total</t>
+          <t>December 31, December</t>
         </is>
       </c>
       <c r="D313" t="inlineStr"/>
-      <c r="E313" s="5" t="n">
-        <v>0.842697</v>
+      <c r="E313" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="F313" s="5" t="n">
-        <v>1</v>
+        <v>0.002019</v>
       </c>
       <c r="G313" s="5" t="n">
-        <v>1</v>
+        <v>3.1e-05</v>
       </c>
       <c r="H313" t="inlineStr">
         <is>
@@ -24123,25 +24085,27 @@
       </c>
       <c r="B314" t="inlineStr">
         <is>
-          <t>diluted</t>
+          <t>Expenses</t>
         </is>
       </c>
       <c r="C314" t="inlineStr">
         <is>
-          <t>For the Years Ended December 31, 2020 and December</t>
-        </is>
-      </c>
-      <c r="D314" t="inlineStr"/>
-      <c r="E314" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>Professional Fees $</t>
+        </is>
+      </c>
+      <c r="D314" t="inlineStr">
+        <is>
+          <t>ProfessionalExpenseAndContractServicesExpense</t>
+        </is>
+      </c>
+      <c r="E314" s="5" t="n">
+        <v>0.138423</v>
       </c>
       <c r="F314" s="5" t="n">
-        <v>0.002019</v>
+        <v>0.222292</v>
       </c>
       <c r="G314" s="5" t="n">
-        <v>3.1e-05</v>
+        <v>0.147144</v>
       </c>
       <c r="H314" t="inlineStr">
         <is>
@@ -24182,12 +24146,12 @@
       </c>
       <c r="B315" t="inlineStr">
         <is>
-          <t>Operating</t>
+          <t>Expenses</t>
         </is>
       </c>
       <c r="C315" t="inlineStr">
         <is>
-          <t>Net loss for the year $</t>
+          <t>Net loss and comprehensive loss for the year $</t>
         </is>
       </c>
       <c r="D315" t="inlineStr">
@@ -24245,23 +24209,29 @@
       </c>
       <c r="B316" t="inlineStr">
         <is>
-          <t>Operating</t>
+          <t>Expenses</t>
         </is>
       </c>
       <c r="C316" t="inlineStr">
         <is>
-          <t>Change in accrued liabilities</t>
-        </is>
-      </c>
-      <c r="D316" t="inlineStr"/>
-      <c r="E316" s="5" t="n">
-        <v>0.01013</v>
+          <t>Net loss per share – basic and diluted $</t>
+        </is>
+      </c>
+      <c r="D316" t="inlineStr">
+        <is>
+          <t>BasicEPS</t>
+        </is>
+      </c>
+      <c r="E316" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="F316" s="5" t="n">
-        <v>-0.004403</v>
+        <v>-2.4e-07</v>
       </c>
       <c r="G316" s="5" t="n">
-        <v>0.124224</v>
+        <v>-1.6e-07</v>
       </c>
       <c r="H316" t="inlineStr">
         <is>
@@ -24302,23 +24272,23 @@
       </c>
       <c r="B317" t="inlineStr">
         <is>
-          <t>Operating</t>
+          <t>diluted</t>
         </is>
       </c>
       <c r="C317" t="inlineStr">
         <is>
-          <t>Cash used in operating activities</t>
+          <t>diluted total</t>
         </is>
       </c>
       <c r="D317" t="inlineStr"/>
       <c r="E317" s="5" t="n">
-        <v>-0.159157</v>
+        <v>0.842697</v>
       </c>
       <c r="F317" s="5" t="n">
-        <v>-0.245543</v>
+        <v>1</v>
       </c>
       <c r="G317" s="5" t="n">
-        <v>-0.035106</v>
+        <v>1</v>
       </c>
       <c r="H317" t="inlineStr">
         <is>
@@ -24359,12 +24329,12 @@
       </c>
       <c r="B318" t="inlineStr">
         <is>
-          <t>Operating</t>
+          <t>diluted</t>
         </is>
       </c>
       <c r="C318" t="inlineStr">
         <is>
-          <t>Net change in cash</t>
+          <t>For the Years Ended December 31, 2020 and December</t>
         </is>
       </c>
       <c r="D318" t="inlineStr"/>
@@ -24374,10 +24344,10 @@
         </is>
       </c>
       <c r="F318" s="5" t="n">
-        <v>-0.245543</v>
+        <v>0.002019</v>
       </c>
       <c r="G318" s="5" t="n">
-        <v>-0.035106</v>
+        <v>3.1e-05</v>
       </c>
       <c r="H318" t="inlineStr">
         <is>
@@ -24423,20 +24393,24 @@
       </c>
       <c r="C319" t="inlineStr">
         <is>
-          <t>Cash beginning of the year</t>
-        </is>
-      </c>
-      <c r="D319" t="inlineStr"/>
+          <t>Net loss for the year $</t>
+        </is>
+      </c>
+      <c r="D319" t="inlineStr">
+        <is>
+          <t>NetIncome</t>
+        </is>
+      </c>
       <c r="E319" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
       <c r="F319" s="5" t="n">
-        <v>0.518641</v>
+        <v>-0.24114</v>
       </c>
       <c r="G319" s="5" t="n">
-        <v>0.273098</v>
+        <v>-0.15933</v>
       </c>
       <c r="H319" t="inlineStr">
         <is>
@@ -24482,20 +24456,18 @@
       </c>
       <c r="C320" t="inlineStr">
         <is>
-          <t>Cash, end of year $</t>
+          <t>Change in accrued liabilities</t>
         </is>
       </c>
       <c r="D320" t="inlineStr"/>
-      <c r="E320" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="E320" s="5" t="n">
+        <v>0.01013</v>
       </c>
       <c r="F320" s="5" t="n">
-        <v>0.273098</v>
+        <v>-0.004403</v>
       </c>
       <c r="G320" s="5" t="n">
-        <v>0.237992</v>
+        <v>0.124224</v>
       </c>
       <c r="H320" t="inlineStr">
         <is>
@@ -24541,20 +24513,18 @@
       </c>
       <c r="C321" t="inlineStr">
         <is>
-          <t>For the Years Ended December 31, 2020 and December</t>
+          <t>Cash used in operating activities</t>
         </is>
       </c>
       <c r="D321" t="inlineStr"/>
-      <c r="E321" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="E321" s="5" t="n">
+        <v>-0.159157</v>
       </c>
       <c r="F321" s="5" t="n">
-        <v>0.002019</v>
+        <v>-0.245543</v>
       </c>
       <c r="G321" s="5" t="n">
-        <v>3.1e-05</v>
+        <v>-0.035106</v>
       </c>
       <c r="H321" t="inlineStr">
         <is>
@@ -24595,12 +24565,12 @@
       </c>
       <c r="B322" t="inlineStr">
         <is>
-          <t>Balance, January 1,</t>
+          <t>Operating</t>
         </is>
       </c>
       <c r="C322" t="inlineStr">
         <is>
-          <t>Balance, January 1,</t>
+          <t>Net change in cash</t>
         </is>
       </c>
       <c r="D322" t="inlineStr"/>
@@ -24610,10 +24580,10 @@
         </is>
       </c>
       <c r="F322" s="5" t="n">
-        <v>0.508511</v>
+        <v>-0.245543</v>
       </c>
       <c r="G322" s="5" t="n">
-        <v>-0.244206</v>
+        <v>-0.035106</v>
       </c>
       <c r="H322" t="inlineStr">
         <is>
@@ -24654,29 +24624,25 @@
       </c>
       <c r="B323" t="inlineStr">
         <is>
-          <t>Balance, January 1,</t>
+          <t>Operating</t>
         </is>
       </c>
       <c r="C323" t="inlineStr">
         <is>
-          <t>Net loss for the year - - -</t>
-        </is>
-      </c>
-      <c r="D323" t="inlineStr">
-        <is>
-          <t>NetIncome</t>
-        </is>
-      </c>
+          <t>Cash beginning of the year</t>
+        </is>
+      </c>
+      <c r="D323" t="inlineStr"/>
       <c r="E323" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
       <c r="F323" s="5" t="n">
-        <v>-0.24114</v>
+        <v>0.518641</v>
       </c>
       <c r="G323" s="5" t="n">
-        <v>-0.24114</v>
+        <v>0.273098</v>
       </c>
       <c r="H323" t="inlineStr">
         <is>
@@ -24717,12 +24683,12 @@
       </c>
       <c r="B324" t="inlineStr">
         <is>
-          <t>Balance, December</t>
+          <t>Operating</t>
         </is>
       </c>
       <c r="C324" t="inlineStr">
         <is>
-          <t>Balance, December</t>
+          <t>Cash, end of year $</t>
         </is>
       </c>
       <c r="D324" t="inlineStr"/>
@@ -24732,10 +24698,10 @@
         </is>
       </c>
       <c r="F324" s="5" t="n">
-        <v>0.267371</v>
+        <v>0.273098</v>
       </c>
       <c r="G324" s="5" t="n">
-        <v>-0.485346</v>
+        <v>0.237992</v>
       </c>
       <c r="H324" t="inlineStr">
         <is>
@@ -24776,12 +24742,12 @@
       </c>
       <c r="B325" t="inlineStr">
         <is>
-          <t>Balance, December</t>
+          <t>Operating</t>
         </is>
       </c>
       <c r="C325" t="inlineStr">
         <is>
-          <t>Balance, December total</t>
+          <t>For the Years Ended December 31, 2020 and December</t>
         </is>
       </c>
       <c r="D325" t="inlineStr"/>
@@ -24835,29 +24801,25 @@
       </c>
       <c r="B326" t="inlineStr">
         <is>
-          <t>Balance, December</t>
+          <t>Balance, January 1,</t>
         </is>
       </c>
       <c r="C326" t="inlineStr">
         <is>
-          <t>Net loss for the year</t>
-        </is>
-      </c>
-      <c r="D326" t="inlineStr">
-        <is>
-          <t>NetIncome</t>
-        </is>
-      </c>
+          <t>Balance, January 1,</t>
+        </is>
+      </c>
+      <c r="D326" t="inlineStr"/>
       <c r="E326" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
       <c r="F326" s="5" t="n">
-        <v>-0.15933</v>
+        <v>0.508511</v>
       </c>
       <c r="G326" s="5" t="n">
-        <v>-0.15933</v>
+        <v>-0.244206</v>
       </c>
       <c r="H326" t="inlineStr">
         <is>
@@ -24896,23 +24858,31 @@
           <t>income_statement</t>
         </is>
       </c>
-      <c r="B327" t="inlineStr"/>
+      <c r="B327" t="inlineStr">
+        <is>
+          <t>Balance, January 1,</t>
+        </is>
+      </c>
       <c r="C327" t="inlineStr">
         <is>
-          <t>9, 2018) to December</t>
-        </is>
-      </c>
-      <c r="D327" t="inlineStr"/>
-      <c r="E327" s="5" t="n">
-        <v>0.002018</v>
+          <t>Net loss for the year - - -</t>
+        </is>
+      </c>
+      <c r="D327" t="inlineStr">
+        <is>
+          <t>NetIncome</t>
+        </is>
+      </c>
+      <c r="E327" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="F327" s="5" t="n">
-        <v>3.1e-05</v>
-      </c>
-      <c r="G327" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>-0.24114</v>
+      </c>
+      <c r="G327" s="5" t="n">
+        <v>-0.24114</v>
       </c>
       <c r="H327" t="inlineStr">
         <is>
@@ -24953,25 +24923,25 @@
       </c>
       <c r="B328" t="inlineStr">
         <is>
-          <t>ended December    ended December</t>
+          <t>Balance, December</t>
         </is>
       </c>
       <c r="C328" t="inlineStr">
         <is>
-          <t>ended December    ended December</t>
+          <t>Balance, December</t>
         </is>
       </c>
       <c r="D328" t="inlineStr"/>
-      <c r="E328" s="5" t="n">
-        <v>0.002018</v>
+      <c r="E328" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="F328" s="5" t="n">
-        <v>3.1e-05</v>
-      </c>
-      <c r="G328" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>0.267371</v>
+      </c>
+      <c r="G328" s="5" t="n">
+        <v>-0.485346</v>
       </c>
       <c r="H328" t="inlineStr">
         <is>
@@ -25012,27 +24982,25 @@
       </c>
       <c r="B329" t="inlineStr">
         <is>
-          <t>Expenses</t>
+          <t>Balance, December</t>
         </is>
       </c>
       <c r="C329" t="inlineStr">
         <is>
-          <t>Stock-based compensation (Note 3)</t>
+          <t>Balance, December total</t>
         </is>
       </c>
       <c r="D329" t="inlineStr"/>
-      <c r="E329" s="5" t="n">
-        <v>0.074919</v>
-      </c>
-      <c r="F329" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G329" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="E329" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F329" s="5" t="n">
+        <v>0.002019</v>
+      </c>
+      <c r="G329" s="5" t="n">
+        <v>3.1e-05</v>
       </c>
       <c r="H329" t="inlineStr">
         <is>
@@ -25073,12 +25041,12 @@
       </c>
       <c r="B330" t="inlineStr">
         <is>
-          <t>Expenses</t>
+          <t>Balance, December</t>
         </is>
       </c>
       <c r="C330" t="inlineStr">
         <is>
-          <t>Net loss and comprehensive loss for the year / $</t>
+          <t>Net loss for the year</t>
         </is>
       </c>
       <c r="D330" t="inlineStr">
@@ -25086,16 +25054,16 @@
           <t>NetIncome</t>
         </is>
       </c>
-      <c r="E330" s="5" t="n">
-        <v>-0.244206</v>
+      <c r="E330" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="F330" s="5" t="n">
-        <v>-0.24114</v>
-      </c>
-      <c r="G330" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>-0.15933</v>
+      </c>
+      <c r="G330" s="5" t="n">
+        <v>-0.15933</v>
       </c>
       <c r="H330" t="inlineStr">
         <is>
@@ -25134,26 +25102,18 @@
           <t>income_statement</t>
         </is>
       </c>
-      <c r="B331" t="inlineStr">
-        <is>
-          <t>period</t>
-        </is>
-      </c>
+      <c r="B331" t="inlineStr"/>
       <c r="C331" t="inlineStr">
         <is>
-          <t>Net loss per share – basic and diluted $</t>
-        </is>
-      </c>
-      <c r="D331" t="inlineStr">
-        <is>
-          <t>BasicEPS</t>
-        </is>
-      </c>
+          <t>9, 2018) to December</t>
+        </is>
+      </c>
+      <c r="D331" t="inlineStr"/>
       <c r="E331" s="5" t="n">
-        <v>-2.9e-07</v>
+        <v>0.002018</v>
       </c>
       <c r="F331" s="5" t="n">
-        <v>-2.4e-07</v>
+        <v>3.1e-05</v>
       </c>
       <c r="G331" t="inlineStr">
         <is>
@@ -25199,24 +25159,20 @@
       </c>
       <c r="B332" t="inlineStr">
         <is>
-          <t>Operating</t>
+          <t>ended December    ended December</t>
         </is>
       </c>
       <c r="C332" t="inlineStr">
         <is>
-          <t>Net loss for the year / period $</t>
-        </is>
-      </c>
-      <c r="D332" t="inlineStr">
-        <is>
-          <t>NetIncome</t>
-        </is>
-      </c>
+          <t>ended December    ended December</t>
+        </is>
+      </c>
+      <c r="D332" t="inlineStr"/>
       <c r="E332" s="5" t="n">
-        <v>-0.244206</v>
+        <v>0.002018</v>
       </c>
       <c r="F332" s="5" t="n">
-        <v>-0.24114</v>
+        <v>3.1e-05</v>
       </c>
       <c r="G332" t="inlineStr">
         <is>
@@ -25262,12 +25218,12 @@
       </c>
       <c r="B333" t="inlineStr">
         <is>
-          <t>Operating</t>
+          <t>Expenses</t>
         </is>
       </c>
       <c r="C333" t="inlineStr">
         <is>
-          <t>Stock-based compensation</t>
+          <t>Stock-based compensation (Note 3)</t>
         </is>
       </c>
       <c r="D333" t="inlineStr"/>
@@ -25323,22 +25279,24 @@
       </c>
       <c r="B334" t="inlineStr">
         <is>
-          <t>Financing</t>
+          <t>Expenses</t>
         </is>
       </c>
       <c r="C334" t="inlineStr">
         <is>
-          <t>Share subscription</t>
-        </is>
-      </c>
-      <c r="D334" t="inlineStr"/>
+          <t>Net loss and comprehensive loss for the year / $</t>
+        </is>
+      </c>
+      <c r="D334" t="inlineStr">
+        <is>
+          <t>NetIncome</t>
+        </is>
+      </c>
       <c r="E334" s="5" t="n">
-        <v>0.75</v>
-      </c>
-      <c r="F334" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>-0.244206</v>
+      </c>
+      <c r="F334" s="5" t="n">
+        <v>-0.24114</v>
       </c>
       <c r="G334" t="inlineStr">
         <is>
@@ -25384,22 +25342,24 @@
       </c>
       <c r="B335" t="inlineStr">
         <is>
-          <t>Financing</t>
+          <t>period</t>
         </is>
       </c>
       <c r="C335" t="inlineStr">
         <is>
-          <t>Cash issuance costs</t>
-        </is>
-      </c>
-      <c r="D335" t="inlineStr"/>
+          <t>Net loss per share – basic and diluted $</t>
+        </is>
+      </c>
+      <c r="D335" t="inlineStr">
+        <is>
+          <t>BasicEPS</t>
+        </is>
+      </c>
       <c r="E335" s="5" t="n">
-        <v>-0.072202</v>
-      </c>
-      <c r="F335" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>-2.9e-07</v>
+      </c>
+      <c r="F335" s="5" t="n">
+        <v>-2.4e-07</v>
       </c>
       <c r="G335" t="inlineStr">
         <is>
@@ -25445,22 +25405,24 @@
       </c>
       <c r="B336" t="inlineStr">
         <is>
-          <t>Financing</t>
+          <t>Operating</t>
         </is>
       </c>
       <c r="C336" t="inlineStr">
         <is>
-          <t>Cash provided by financing activities</t>
-        </is>
-      </c>
-      <c r="D336" t="inlineStr"/>
+          <t>Net loss for the year / period $</t>
+        </is>
+      </c>
+      <c r="D336" t="inlineStr">
+        <is>
+          <t>NetIncome</t>
+        </is>
+      </c>
       <c r="E336" s="5" t="n">
-        <v>0.677798</v>
-      </c>
-      <c r="F336" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>-0.244206</v>
+      </c>
+      <c r="F336" s="5" t="n">
+        <v>-0.24114</v>
       </c>
       <c r="G336" t="inlineStr">
         <is>
@@ -25506,20 +25468,22 @@
       </c>
       <c r="B337" t="inlineStr">
         <is>
-          <t>Financing</t>
+          <t>Operating</t>
         </is>
       </c>
       <c r="C337" t="inlineStr">
         <is>
-          <t>Net change in cash</t>
+          <t>Stock-based compensation</t>
         </is>
       </c>
       <c r="D337" t="inlineStr"/>
       <c r="E337" s="5" t="n">
-        <v>0.518641</v>
-      </c>
-      <c r="F337" s="5" t="n">
-        <v>-0.245543</v>
+        <v>0.074919</v>
+      </c>
+      <c r="F337" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="G337" t="inlineStr">
         <is>
@@ -25570,17 +25534,17 @@
       </c>
       <c r="C338" t="inlineStr">
         <is>
-          <t>Cash beginning of the year / period</t>
+          <t>Share subscription</t>
         </is>
       </c>
       <c r="D338" t="inlineStr"/>
-      <c r="E338" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F338" s="5" t="n">
-        <v>0.518641</v>
+      <c r="E338" s="5" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="F338" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="G338" t="inlineStr">
         <is>
@@ -25631,15 +25595,17 @@
       </c>
       <c r="C339" t="inlineStr">
         <is>
-          <t>Cash, end of year / period $</t>
+          <t>Cash issuance costs</t>
         </is>
       </c>
       <c r="D339" t="inlineStr"/>
       <c r="E339" s="5" t="n">
-        <v>0.518641</v>
-      </c>
-      <c r="F339" s="5" t="n">
-        <v>0.273098</v>
+        <v>-0.072202</v>
+      </c>
+      <c r="F339" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="G339" t="inlineStr">
         <is>
@@ -25690,15 +25656,17 @@
       </c>
       <c r="C340" t="inlineStr">
         <is>
-          <t>9, 2018) to December</t>
+          <t>Cash provided by financing activities</t>
         </is>
       </c>
       <c r="D340" t="inlineStr"/>
       <c r="E340" s="5" t="n">
-        <v>0.002018</v>
-      </c>
-      <c r="F340" s="5" t="n">
-        <v>3.1e-05</v>
+        <v>0.677798</v>
+      </c>
+      <c r="F340" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="G340" t="inlineStr">
         <is>
@@ -25744,24 +25712,20 @@
       </c>
       <c r="B341" t="inlineStr">
         <is>
-          <t>Shares      Capital        surplus        Deficit         Equity</t>
+          <t>Financing</t>
         </is>
       </c>
       <c r="C341" t="inlineStr">
         <is>
-          <t>Balance, January 9, 2018 - $ - $ - $</t>
+          <t>Net change in cash</t>
         </is>
       </c>
       <c r="D341" t="inlineStr"/>
-      <c r="E341" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F341" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="E341" s="5" t="n">
+        <v>0.518641</v>
+      </c>
+      <c r="F341" s="5" t="n">
+        <v>-0.245543</v>
       </c>
       <c r="G341" t="inlineStr">
         <is>
@@ -25807,22 +25771,22 @@
       </c>
       <c r="B342" t="inlineStr">
         <is>
-          <t>Shares      Capital        surplus        Deficit         Equity</t>
+          <t>Financing</t>
         </is>
       </c>
       <c r="C342" t="inlineStr">
         <is>
-          <t>Share subscription (Note 3) 1,000,000 250,000 -</t>
+          <t>Cash beginning of the year / period</t>
         </is>
       </c>
       <c r="D342" t="inlineStr"/>
-      <c r="E342" s="5" t="n">
-        <v>0.25</v>
-      </c>
-      <c r="F342" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="E342" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F342" s="5" t="n">
+        <v>0.518641</v>
       </c>
       <c r="G342" t="inlineStr">
         <is>
@@ -25868,22 +25832,20 @@
       </c>
       <c r="B343" t="inlineStr">
         <is>
-          <t>Shares      Capital        surplus        Deficit         Equity</t>
+          <t>Financing</t>
         </is>
       </c>
       <c r="C343" t="inlineStr">
         <is>
-          <t>Initial public offering (Note 3) 1,000,000 500,000 -</t>
+          <t>Cash, end of year / period $</t>
         </is>
       </c>
       <c r="D343" t="inlineStr"/>
       <c r="E343" s="5" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="F343" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>0.518641</v>
+      </c>
+      <c r="F343" s="5" t="n">
+        <v>0.273098</v>
       </c>
       <c r="G343" t="inlineStr">
         <is>
@@ -25929,22 +25891,20 @@
       </c>
       <c r="B344" t="inlineStr">
         <is>
-          <t>Shares      Capital        surplus        Deficit         Equity</t>
+          <t>Financing</t>
         </is>
       </c>
       <c r="C344" t="inlineStr">
         <is>
-          <t>Cost of issuance-Cash - (72,202) -</t>
+          <t>9, 2018) to December</t>
         </is>
       </c>
       <c r="D344" t="inlineStr"/>
       <c r="E344" s="5" t="n">
-        <v>-0.072202</v>
-      </c>
-      <c r="F344" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>0.002018</v>
+      </c>
+      <c r="F344" s="5" t="n">
+        <v>3.1e-05</v>
       </c>
       <c r="G344" t="inlineStr">
         <is>
@@ -25990,12 +25950,12 @@
       </c>
       <c r="B345" t="inlineStr">
         <is>
-          <t>Cost of issuance-Agent</t>
+          <t>Shares      Capital        surplus        Deficit         Equity</t>
         </is>
       </c>
       <c r="C345" t="inlineStr">
         <is>
-          <t>Warrants issued on IPO - (26,444) 26,444</t>
+          <t>Balance, January 9, 2018 - $ - $ - $</t>
         </is>
       </c>
       <c r="D345" t="inlineStr"/>
@@ -26053,17 +26013,17 @@
       </c>
       <c r="B346" t="inlineStr">
         <is>
-          <t>Stock-based compensation</t>
+          <t>Shares      Capital        surplus        Deficit         Equity</t>
         </is>
       </c>
       <c r="C346" t="inlineStr">
         <is>
-          <t>Stock-based compensation</t>
+          <t>Share subscription (Note 3) 1,000,000 250,000 -</t>
         </is>
       </c>
       <c r="D346" t="inlineStr"/>
       <c r="E346" s="5" t="n">
-        <v>0.074919</v>
+        <v>0.25</v>
       </c>
       <c r="F346" t="inlineStr">
         <is>
@@ -26114,24 +26074,22 @@
       </c>
       <c r="B347" t="inlineStr">
         <is>
-          <t>Stock-based compensation</t>
+          <t>Shares      Capital        surplus        Deficit         Equity</t>
         </is>
       </c>
       <c r="C347" t="inlineStr">
         <is>
-          <t>Net loss for the period - - -</t>
-        </is>
-      </c>
-      <c r="D347" t="inlineStr">
-        <is>
-          <t>NetIncome</t>
-        </is>
-      </c>
+          <t>Initial public offering (Note 3) 1,000,000 500,000 -</t>
+        </is>
+      </c>
+      <c r="D347" t="inlineStr"/>
       <c r="E347" s="5" t="n">
-        <v>-0.244206</v>
-      </c>
-      <c r="F347" s="5" t="n">
-        <v>-0.244206</v>
+        <v>0.5</v>
+      </c>
+      <c r="F347" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="G347" t="inlineStr">
         <is>
@@ -26177,20 +26135,22 @@
       </c>
       <c r="B348" t="inlineStr">
         <is>
-          <t>Stock-based compensation</t>
+          <t>Shares      Capital        surplus        Deficit         Equity</t>
         </is>
       </c>
       <c r="C348" t="inlineStr">
         <is>
-          <t>Balance, December 31, 2018 2,000,000 $ 651,354 $101,363 $</t>
+          <t>Cost of issuance-Cash - (72,202) -</t>
         </is>
       </c>
       <c r="D348" t="inlineStr"/>
       <c r="E348" s="5" t="n">
-        <v>0.508511</v>
-      </c>
-      <c r="F348" s="5" t="n">
-        <v>-0.244206</v>
+        <v>-0.072202</v>
+      </c>
+      <c r="F348" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="G348" t="inlineStr">
         <is>
@@ -26236,20 +26196,24 @@
       </c>
       <c r="B349" t="inlineStr">
         <is>
-          <t>Stock-based compensation</t>
+          <t>Cost of issuance-Agent</t>
         </is>
       </c>
       <c r="C349" t="inlineStr">
         <is>
-          <t>Balance at January 1, 2019 2,000,000 $ 651,354 $ 101,363 $</t>
+          <t>Warrants issued on IPO - (26,444) 26,444</t>
         </is>
       </c>
       <c r="D349" t="inlineStr"/>
-      <c r="E349" s="5" t="n">
-        <v>0.508511</v>
-      </c>
-      <c r="F349" s="5" t="n">
-        <v>-0.244206</v>
+      <c r="E349" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F349" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="G349" t="inlineStr">
         <is>
@@ -26300,19 +26264,17 @@
       </c>
       <c r="C350" t="inlineStr">
         <is>
-          <t>Net loss for the year - - -</t>
-        </is>
-      </c>
-      <c r="D350" t="inlineStr">
-        <is>
-          <t>NetIncome</t>
-        </is>
-      </c>
+          <t>Stock-based compensation</t>
+        </is>
+      </c>
+      <c r="D350" t="inlineStr"/>
       <c r="E350" s="5" t="n">
-        <v>-0.24114</v>
-      </c>
-      <c r="F350" s="5" t="n">
-        <v>-0.24114</v>
+        <v>0.074919</v>
+      </c>
+      <c r="F350" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="G350" t="inlineStr">
         <is>
@@ -26363,47 +26325,291 @@
       </c>
       <c r="C351" t="inlineStr">
         <is>
+          <t>Net loss for the period - - -</t>
+        </is>
+      </c>
+      <c r="D351" t="inlineStr">
+        <is>
+          <t>NetIncome</t>
+        </is>
+      </c>
+      <c r="E351" s="5" t="n">
+        <v>-0.244206</v>
+      </c>
+      <c r="F351" s="5" t="n">
+        <v>-0.244206</v>
+      </c>
+      <c r="G351" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H351" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I351" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J351" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K351" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L351" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M351" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="352">
+      <c r="A352" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B352" t="inlineStr">
+        <is>
+          <t>Stock-based compensation</t>
+        </is>
+      </c>
+      <c r="C352" t="inlineStr">
+        <is>
+          <t>Balance, December 31, 2018 2,000,000 $ 651,354 $101,363 $</t>
+        </is>
+      </c>
+      <c r="D352" t="inlineStr"/>
+      <c r="E352" s="5" t="n">
+        <v>0.508511</v>
+      </c>
+      <c r="F352" s="5" t="n">
+        <v>-0.244206</v>
+      </c>
+      <c r="G352" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H352" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I352" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J352" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K352" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L352" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M352" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="353">
+      <c r="A353" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B353" t="inlineStr">
+        <is>
+          <t>Stock-based compensation</t>
+        </is>
+      </c>
+      <c r="C353" t="inlineStr">
+        <is>
+          <t>Balance at January 1, 2019 2,000,000 $ 651,354 $ 101,363 $</t>
+        </is>
+      </c>
+      <c r="D353" t="inlineStr"/>
+      <c r="E353" s="5" t="n">
+        <v>0.508511</v>
+      </c>
+      <c r="F353" s="5" t="n">
+        <v>-0.244206</v>
+      </c>
+      <c r="G353" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H353" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I353" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J353" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K353" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L353" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M353" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="354">
+      <c r="A354" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B354" t="inlineStr">
+        <is>
+          <t>Stock-based compensation</t>
+        </is>
+      </c>
+      <c r="C354" t="inlineStr">
+        <is>
+          <t>Net loss for the year - - -</t>
+        </is>
+      </c>
+      <c r="D354" t="inlineStr">
+        <is>
+          <t>NetIncome</t>
+        </is>
+      </c>
+      <c r="E354" s="5" t="n">
+        <v>-0.24114</v>
+      </c>
+      <c r="F354" s="5" t="n">
+        <v>-0.24114</v>
+      </c>
+      <c r="G354" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H354" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I354" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J354" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K354" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L354" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M354" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="355">
+      <c r="A355" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B355" t="inlineStr">
+        <is>
+          <t>Stock-based compensation</t>
+        </is>
+      </c>
+      <c r="C355" t="inlineStr">
+        <is>
           <t>Balance, December 31, 2019 2,000,000 651,354 101,363 $</t>
         </is>
       </c>
-      <c r="D351" t="inlineStr"/>
-      <c r="E351" s="5" t="n">
+      <c r="D355" t="inlineStr"/>
+      <c r="E355" s="5" t="n">
         <v>0.267371</v>
       </c>
-      <c r="F351" s="5" t="n">
+      <c r="F355" s="5" t="n">
         <v>-0.485346</v>
       </c>
-      <c r="G351" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H351" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I351" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J351" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K351" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L351" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="M351" t="inlineStr">
+      <c r="G355" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H355" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I355" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J355" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K355" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L355" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M355" t="inlineStr">
         <is>
           <t>-</t>
         </is>
